--- a/chemical_code/化工测试数据.xlsx
+++ b/chemical_code/化工测试数据.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\21133\Documents\GitHub\learning-git\chemical_code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEFFADFE-C0C1-4913-907E-F01B66E24043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4DD2D5A-E295-4B14-A797-4816AC2F475E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -559,7 +559,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="1">
-        <v>555</v>
+        <v>339</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" si="2"/>
